--- a/quizzes/022_volunteer_award_category_quiz--quizzes.xlsx
+++ b/quizzes/022_volunteer_award_category_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -815,8 +815,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,12 +844,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'arts_and_culture'}</t>
+          <t>arts_and_culture</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Arts and Culture'}</t>
+          <t>Arts and Culture</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'community_development'}</t>
+          <t>community_development</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Community Development'}</t>
+          <t>Community Development</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'health_and_wellness'}</t>
+          <t>health_and_wellness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Health and Wellness'}</t>
+          <t>Health and Wellness</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'humanitarian_aid'}</t>
+          <t>humanitarian_aid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Humanitarian Aid'}</t>
+          <t>Humanitarian Aid</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'arts_and_culture',_'label':_'arts_and_culture'}</t>
+          <t>arts_and_culture</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Arts and Culture', 'label': 'Arts and Culture'}</t>
+          <t>Arts and Culture</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'community_development',_'label':_'community_development'}</t>
+          <t>community_development</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Community Development', 'label': 'Community Development'}</t>
+          <t>Community Development</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'education',_'label':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Education', 'label': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'health_and_wellness',_'label':_'health_and_wellness'}</t>
+          <t>health_and_wellness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Health and Wellness', 'label': 'Health and Wellness'}</t>
+          <t>Health and Wellness</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'humanitarian_aid',_'label':_'humanitarian_aid'}</t>
+          <t>humanitarian_aid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Humanitarian Aid', 'label': 'Humanitarian Aid'}</t>
+          <t>Humanitarian Aid</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'to_help_others'}</t>
+          <t>to_help_others</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'To help others'}</t>
+          <t>To help others</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'to_learn_something_new'}</t>
+          <t>to_learn_something_new</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'To learn something new'}</t>
+          <t>To learn something new</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'to_make_a_difference'}</t>
+          <t>to_make_a_difference</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'To make a difference'}</t>
+          <t>To make a difference</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'to_meet_new_people'}</t>
+          <t>to_meet_new_people</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'To meet new people'}</t>
+          <t>To meet new people</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'to_satisfy_my_personal_values'}</t>
+          <t>to_satisfy_my_personal_values</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'To satisfy my personal values'}</t>
+          <t>To satisfy my personal values</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'to_volunteer_with_friends'}</t>
+          <t>to_volunteer_with_friends</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'To volunteer with friends'}</t>
+          <t>To volunteer with friends</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'to_see_the_impact_of_my_work'}</t>
+          <t>to_see_the_impact_of_my_work</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'To see the impact of my work'}</t>
+          <t>To see the impact of my work</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'to_serve_a_higher_purpose'}</t>
+          <t>to_serve_a_higher_purpose</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'To serve a higher purpose'}</t>
+          <t>To serve a higher purpose</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'to_have_fun'}</t>
+          <t>to_have_fun</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'To have fun'}</t>
+          <t>To have fun</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'to_develop_skills'}</t>
+          <t>to_develop_skills</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'To develop skills'}</t>
+          <t>To develop skills</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'to_get_involved_in_the_community'}</t>
+          <t>to_get_involved_in_the_community</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'To get involved in the community'}</t>
+          <t>To get involved in the community</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'to_feel_good_about_myself'}</t>
+          <t>to_feel_good_about_myself</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'To feel good about myself'}</t>
+          <t>To feel good about myself</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'to_get_out_of_my_house'}</t>
+          <t>to_get_out_of_my_house</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'To get out of my house'}</t>
+          <t>To get out of my house</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'to_be_part_of_something_bigger_than_myself'}</t>
+          <t>to_be_part_of_something_bigger_than_myself</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'To be part of something bigger than myself'}</t>
+          <t>To be part of something bigger than myself</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'to_be_of_service'}</t>
+          <t>to_be_of_service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'To be of service'}</t>
+          <t>To be of service</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'to_make_new_connections'}</t>
+          <t>to_make_new_connections</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'To make new connections'}</t>
+          <t>To make new connections</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'to_be_of_use'}</t>
+          <t>to_be_of_use</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'To be of use'}</t>
+          <t>To be of use</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'1-5',_'label':_'1-5_times'}</t>
+          <t>1-5_times</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': '1-5', 'label': '1-5 times'}</t>
+          <t>1-5 times</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_5',_'label':_'more_than_5'}</t>
+          <t>more_than_5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'More than 5', 'label': 'More than 5'}</t>
+          <t>More than 5</t>
         </is>
       </c>
     </row>
